--- a/シフト（自動化）.xlsx
+++ b/シフト（自動化）.xlsx
@@ -5,10 +5,10 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\フレシード齊田\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\フレシード齊田\Desktop\AI関係\シフト自動化\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0C16DE11-5E2B-41CA-9F3D-D8C58576B86D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AA18F0B3-EA9F-457A-8F11-60923EEAEF54}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{6B8549B6-0C67-4ED0-92E9-E992FA3609B3}"/>
   </bookViews>
@@ -336,7 +336,7 @@
     <numFmt numFmtId="178" formatCode="d&quot;&quot;"/>
     <numFmt numFmtId="179" formatCode="0;\-0;;@"/>
   </numFmts>
-  <fonts count="35" x14ac:knownFonts="1">
+  <fonts count="28" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -384,12 +384,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <name val="UD デジタル 教科書体 N-B"/>
-      <family val="1"/>
-      <charset val="128"/>
-    </font>
-    <font>
       <b/>
       <sz val="11"/>
       <color theme="1"/>
@@ -412,20 +406,6 @@
       <family val="3"/>
       <charset val="128"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color theme="1"/>
-      <name val="UD デジタル 教科書体 N-B"/>
-      <family val="1"/>
-      <charset val="128"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF0099FF"/>
-      <name val="UD デジタル 教科書体 N-B"/>
-      <family val="1"/>
-      <charset val="128"/>
     </font>
     <font>
       <sz val="10"/>
@@ -524,13 +504,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="9"/>
-      <color theme="1"/>
-      <name val="UD デジタル 教科書体 N-B"/>
-      <family val="1"/>
-      <charset val="128"/>
-    </font>
-    <font>
       <b/>
       <sz val="11"/>
       <color theme="1"/>
@@ -569,20 +542,6 @@
       <charset val="128"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color theme="8"/>
-      <name val="UD デジタル 教科書体 N-B"/>
-      <family val="1"/>
-      <charset val="128"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="9"/>
-      <name val="UD デジタル 教科書体 N-B"/>
-      <family val="1"/>
-      <charset val="128"/>
-    </font>
-    <font>
       <u/>
       <sz val="16"/>
       <color theme="1"/>
@@ -599,13 +558,6 @@
       <family val="3"/>
       <charset val="128"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="6"/>
-      <color theme="4"/>
-      <name val="UD デジタル 教科書体 N-B"/>
-      <family val="1"/>
-      <charset val="128"/>
     </font>
   </fonts>
   <fills count="6">
@@ -640,7 +592,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="53">
+  <borders count="47">
     <border>
       <left/>
       <right/>
@@ -747,19 +699,6 @@
       <left style="medium">
         <color indexed="64"/>
       </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom style="hair">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
       <right style="medium">
         <color indexed="64"/>
       </right>
@@ -1246,90 +1185,6 @@
     </border>
     <border>
       <left/>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom style="hair">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right style="thick">
-        <color indexed="64"/>
-      </right>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom style="hair">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right style="thick">
-        <color indexed="64"/>
-      </right>
-      <top style="hair">
-        <color indexed="64"/>
-      </top>
-      <bottom style="hair">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right style="thick">
-        <color indexed="64"/>
-      </right>
-      <top style="hair">
-        <color indexed="64"/>
-      </top>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thick">
-        <color indexed="64"/>
-      </right>
-      <top style="hair">
-        <color indexed="64"/>
-      </top>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right style="thick">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom style="hair">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
       <right/>
       <top style="hair">
         <color indexed="64"/>
@@ -1348,6 +1203,21 @@
         <color indexed="64"/>
       </top>
       <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="hair">
         <color indexed="64"/>
       </bottom>
       <diagonal/>
@@ -1358,7 +1228,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="145">
+  <cellXfs count="117">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1374,424 +1244,340 @@
     <xf numFmtId="177" fontId="1" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="1" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="1" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="1" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="24" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="25" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="1" fillId="0" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="1" fillId="0" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="1" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="1" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="1" fillId="0" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="1" fillId="0" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="31" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="20" fontId="4" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="32" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="20" fontId="4" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="20" fontId="4" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="36" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="20" fontId="4" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="37" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1">
+    <xf numFmtId="178" fontId="20" fillId="0" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="20" fillId="0" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="20" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="20" fillId="0" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1">
+    <xf numFmtId="178" fontId="20" fillId="0" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="20" fillId="0" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="23" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="23" fillId="0" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="23" fillId="0" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="23" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="23" fillId="0" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="23" fillId="0" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="23" fillId="0" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="27" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="27" fillId="0" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="27" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" textRotation="255"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" textRotation="255"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="20" fontId="4" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="31" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="23" fillId="0" borderId="42" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="1" fillId="0" borderId="45" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="1" fillId="0" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="1" fillId="0" borderId="43" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="1" fillId="0" borderId="46" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="1" fillId="0" borderId="47" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="1" fillId="0" borderId="48" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="45" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="50" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="47" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="1" fillId="0" borderId="49" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="43" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="51" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="1" fillId="0" borderId="51" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="34" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="20" fillId="0" borderId="41" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="42" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="44" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+    <xf numFmtId="0" fontId="24" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="52" xfId="0" applyFont="1" applyBorder="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="1" fillId="0" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="1" fillId="0" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="25" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="23" fillId="0" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="1" fillId="0" borderId="46" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="1" fillId="0" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="1" fillId="0" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="22" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="23" fillId="0" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="1" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -4422,7 +4208,7 @@
     <col min="1" max="2" width="3.19921875" style="1" customWidth="1"/>
     <col min="3" max="3" width="9.69921875" style="1" customWidth="1"/>
     <col min="4" max="7" width="4.19921875" style="1" customWidth="1"/>
-    <col min="8" max="8" width="4.19921875" style="69" customWidth="1"/>
+    <col min="8" max="8" width="4.19921875" style="54" customWidth="1"/>
     <col min="9" max="11" width="4.19921875" style="1" customWidth="1"/>
     <col min="12" max="12" width="4.59765625" style="1" customWidth="1"/>
     <col min="13" max="15" width="4.19921875" style="1" customWidth="1"/>
@@ -4431,8 +4217,7 @@
     <col min="18" max="18" width="4.5" style="1" customWidth="1"/>
     <col min="19" max="29" width="4.19921875" style="1" customWidth="1"/>
     <col min="30" max="30" width="4" style="1" customWidth="1"/>
-    <col min="31" max="33" width="4.19921875" style="1" customWidth="1"/>
-    <col min="34" max="34" width="3.69921875" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="34" width="4.19921875" style="1" customWidth="1"/>
     <col min="35" max="35" width="9.69921875" style="1" customWidth="1"/>
     <col min="36" max="36" width="4.19921875" style="1" customWidth="1"/>
     <col min="37" max="37" width="4.3984375" style="1" customWidth="1"/>
@@ -4442,667 +4227,667 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:44" ht="22.5" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="C1" s="124" t="s">
+      <c r="C1" s="93" t="s">
         <v>20</v>
       </c>
-      <c r="D1" s="124"/>
-      <c r="E1" s="124"/>
-      <c r="F1" s="124"/>
-      <c r="G1" s="124"/>
-      <c r="H1" s="124"/>
-      <c r="I1" s="124"/>
-      <c r="J1" s="124"/>
-      <c r="K1" s="124"/>
-      <c r="L1" s="124"/>
-      <c r="M1" s="124"/>
-      <c r="N1" s="124"/>
-      <c r="O1" s="124"/>
-      <c r="P1" s="124"/>
-      <c r="Q1" s="124"/>
-      <c r="R1" s="124"/>
-      <c r="S1" s="124"/>
-      <c r="T1" s="124"/>
-      <c r="U1" s="124"/>
-      <c r="V1" s="124"/>
-      <c r="W1" s="124"/>
-      <c r="X1" s="124"/>
-      <c r="Y1" s="124"/>
-      <c r="Z1" s="124"/>
-      <c r="AA1" s="124"/>
-      <c r="AB1" s="124"/>
-      <c r="AC1" s="124"/>
-      <c r="AD1" s="124"/>
-      <c r="AE1" s="124"/>
-      <c r="AF1" s="124"/>
-      <c r="AG1" s="124"/>
-      <c r="AH1" s="124"/>
+      <c r="D1" s="93"/>
+      <c r="E1" s="93"/>
+      <c r="F1" s="93"/>
+      <c r="G1" s="93"/>
+      <c r="H1" s="93"/>
+      <c r="I1" s="93"/>
+      <c r="J1" s="93"/>
+      <c r="K1" s="93"/>
+      <c r="L1" s="93"/>
+      <c r="M1" s="93"/>
+      <c r="N1" s="93"/>
+      <c r="O1" s="93"/>
+      <c r="P1" s="93"/>
+      <c r="Q1" s="93"/>
+      <c r="R1" s="93"/>
+      <c r="S1" s="93"/>
+      <c r="T1" s="93"/>
+      <c r="U1" s="93"/>
+      <c r="V1" s="93"/>
+      <c r="W1" s="93"/>
+      <c r="X1" s="93"/>
+      <c r="Y1" s="93"/>
+      <c r="Z1" s="93"/>
+      <c r="AA1" s="93"/>
+      <c r="AB1" s="93"/>
+      <c r="AC1" s="93"/>
+      <c r="AD1" s="93"/>
+      <c r="AE1" s="93"/>
+      <c r="AF1" s="93"/>
+      <c r="AG1" s="93"/>
+      <c r="AH1" s="93"/>
     </row>
     <row r="2" spans="1:44" ht="22.5" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="C2" s="122"/>
-      <c r="D2" s="125"/>
-      <c r="E2" s="122"/>
-      <c r="F2" s="122"/>
-      <c r="G2" s="127"/>
-      <c r="H2" s="129"/>
-      <c r="I2" s="131"/>
-      <c r="J2" s="122"/>
-      <c r="K2" s="122"/>
-      <c r="L2" s="133"/>
-      <c r="M2" s="122"/>
-      <c r="N2" s="122"/>
-      <c r="O2" s="73"/>
-      <c r="P2" s="119"/>
-      <c r="Q2" s="71"/>
-      <c r="R2" s="111"/>
-      <c r="S2" s="122"/>
-      <c r="T2" s="122"/>
-      <c r="U2" s="122"/>
-      <c r="V2" s="122"/>
-      <c r="W2" s="122"/>
-      <c r="X2" s="122"/>
-      <c r="Y2" s="122"/>
-      <c r="Z2" s="122"/>
-      <c r="AA2" s="122"/>
-      <c r="AB2" s="122"/>
-      <c r="AC2" s="122"/>
-      <c r="AD2" s="135"/>
-      <c r="AE2" s="137"/>
-      <c r="AF2" s="122"/>
-      <c r="AG2" s="122"/>
-      <c r="AH2" s="47"/>
-      <c r="AI2" s="47"/>
+      <c r="C2" s="87"/>
+      <c r="D2" s="94"/>
+      <c r="E2" s="87"/>
+      <c r="F2" s="87"/>
+      <c r="G2" s="96"/>
+      <c r="H2" s="98"/>
+      <c r="I2" s="100"/>
+      <c r="J2" s="87"/>
+      <c r="K2" s="87"/>
+      <c r="L2" s="102"/>
+      <c r="M2" s="87"/>
+      <c r="N2" s="87"/>
+      <c r="O2" s="57"/>
+      <c r="P2" s="78"/>
+      <c r="Q2" s="55"/>
+      <c r="R2" s="72"/>
+      <c r="S2" s="87"/>
+      <c r="T2" s="87"/>
+      <c r="U2" s="87"/>
+      <c r="V2" s="87"/>
+      <c r="W2" s="87"/>
+      <c r="X2" s="87"/>
+      <c r="Y2" s="87"/>
+      <c r="Z2" s="87"/>
+      <c r="AA2" s="87"/>
+      <c r="AB2" s="87"/>
+      <c r="AC2" s="87"/>
+      <c r="AD2" s="89"/>
+      <c r="AE2" s="91"/>
+      <c r="AF2" s="87"/>
+      <c r="AG2" s="87"/>
+      <c r="AH2" s="38"/>
+      <c r="AI2" s="38"/>
     </row>
     <row r="3" spans="1:44" ht="22.5" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B3" s="49"/>
-      <c r="C3" s="122"/>
-      <c r="D3" s="125"/>
-      <c r="E3" s="122"/>
-      <c r="F3" s="122"/>
-      <c r="G3" s="127"/>
-      <c r="H3" s="129"/>
-      <c r="I3" s="131"/>
-      <c r="J3" s="122"/>
-      <c r="K3" s="122"/>
-      <c r="L3" s="133"/>
-      <c r="M3" s="122"/>
-      <c r="N3" s="122"/>
-      <c r="O3" s="73"/>
-      <c r="P3" s="119"/>
-      <c r="Q3" s="71"/>
-      <c r="R3" s="111"/>
-      <c r="S3" s="122"/>
-      <c r="T3" s="122"/>
-      <c r="U3" s="122"/>
-      <c r="V3" s="122"/>
-      <c r="W3" s="122"/>
-      <c r="X3" s="122"/>
-      <c r="Y3" s="122"/>
-      <c r="Z3" s="122"/>
-      <c r="AA3" s="122"/>
-      <c r="AB3" s="122"/>
-      <c r="AC3" s="122"/>
-      <c r="AD3" s="135"/>
-      <c r="AE3" s="137"/>
-      <c r="AF3" s="122"/>
-      <c r="AG3" s="122"/>
-      <c r="AH3" s="47"/>
-      <c r="AI3" s="47"/>
+      <c r="B3" s="40"/>
+      <c r="C3" s="87"/>
+      <c r="D3" s="94"/>
+      <c r="E3" s="87"/>
+      <c r="F3" s="87"/>
+      <c r="G3" s="96"/>
+      <c r="H3" s="98"/>
+      <c r="I3" s="100"/>
+      <c r="J3" s="87"/>
+      <c r="K3" s="87"/>
+      <c r="L3" s="102"/>
+      <c r="M3" s="87"/>
+      <c r="N3" s="87"/>
+      <c r="O3" s="57"/>
+      <c r="P3" s="78"/>
+      <c r="Q3" s="55"/>
+      <c r="R3" s="72"/>
+      <c r="S3" s="87"/>
+      <c r="T3" s="87"/>
+      <c r="U3" s="87"/>
+      <c r="V3" s="87"/>
+      <c r="W3" s="87"/>
+      <c r="X3" s="87"/>
+      <c r="Y3" s="87"/>
+      <c r="Z3" s="87"/>
+      <c r="AA3" s="87"/>
+      <c r="AB3" s="87"/>
+      <c r="AC3" s="87"/>
+      <c r="AD3" s="89"/>
+      <c r="AE3" s="91"/>
+      <c r="AF3" s="87"/>
+      <c r="AG3" s="87"/>
+      <c r="AH3" s="38"/>
+      <c r="AI3" s="38"/>
     </row>
     <row r="4" spans="1:44" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B4" s="49"/>
-      <c r="C4" s="123"/>
-      <c r="D4" s="126"/>
-      <c r="E4" s="123"/>
-      <c r="F4" s="123"/>
-      <c r="G4" s="128"/>
-      <c r="H4" s="130"/>
-      <c r="I4" s="132"/>
-      <c r="J4" s="123"/>
-      <c r="K4" s="123"/>
-      <c r="L4" s="134"/>
-      <c r="M4" s="123"/>
-      <c r="N4" s="123"/>
-      <c r="O4" s="74"/>
-      <c r="P4" s="120"/>
-      <c r="Q4" s="72"/>
-      <c r="R4" s="112"/>
-      <c r="S4" s="123"/>
-      <c r="T4" s="123"/>
-      <c r="U4" s="123"/>
-      <c r="V4" s="123"/>
-      <c r="W4" s="123"/>
-      <c r="X4" s="123"/>
-      <c r="Y4" s="123"/>
-      <c r="Z4" s="123"/>
-      <c r="AA4" s="123"/>
-      <c r="AB4" s="123"/>
-      <c r="AC4" s="123"/>
-      <c r="AD4" s="136"/>
-      <c r="AE4" s="138"/>
-      <c r="AF4" s="123"/>
-      <c r="AG4" s="123"/>
-      <c r="AH4" s="48"/>
-      <c r="AI4" s="47"/>
+      <c r="B4" s="40"/>
+      <c r="C4" s="88"/>
+      <c r="D4" s="95"/>
+      <c r="E4" s="88"/>
+      <c r="F4" s="88"/>
+      <c r="G4" s="97"/>
+      <c r="H4" s="99"/>
+      <c r="I4" s="101"/>
+      <c r="J4" s="88"/>
+      <c r="K4" s="88"/>
+      <c r="L4" s="103"/>
+      <c r="M4" s="88"/>
+      <c r="N4" s="88"/>
+      <c r="O4" s="58"/>
+      <c r="P4" s="79"/>
+      <c r="Q4" s="56"/>
+      <c r="R4" s="73"/>
+      <c r="S4" s="88"/>
+      <c r="T4" s="88"/>
+      <c r="U4" s="88"/>
+      <c r="V4" s="88"/>
+      <c r="W4" s="88"/>
+      <c r="X4" s="88"/>
+      <c r="Y4" s="88"/>
+      <c r="Z4" s="88"/>
+      <c r="AA4" s="88"/>
+      <c r="AB4" s="88"/>
+      <c r="AC4" s="88"/>
+      <c r="AD4" s="90"/>
+      <c r="AE4" s="92"/>
+      <c r="AF4" s="88"/>
+      <c r="AG4" s="88"/>
+      <c r="AH4" s="39"/>
+      <c r="AI4" s="38"/>
     </row>
     <row r="5" spans="1:44" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="C5" s="46" t="s">
+      <c r="C5" s="37" t="s">
         <v>4</v>
       </c>
-      <c r="D5" s="113">
+      <c r="D5" s="74">
         <f t="shared" ref="D5:AH5" si="0">COUNTIFS(D10:D18,"休")</f>
         <v>0</v>
       </c>
-      <c r="E5" s="44">
+      <c r="E5" s="35">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="F5" s="44">
+      <c r="F5" s="35">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="G5" s="44">
+      <c r="G5" s="35">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="H5" s="64">
+      <c r="H5" s="51">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="I5" s="44">
+      <c r="I5" s="35">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J5" s="44">
+      <c r="J5" s="35">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="K5" s="117">
+      <c r="K5" s="77">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="L5" s="44">
+      <c r="L5" s="35">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="M5" s="44">
+      <c r="M5" s="35">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="N5" s="44">
+      <c r="N5" s="35">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="O5" s="44">
+      <c r="O5" s="35">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="P5" s="44">
+      <c r="P5" s="35">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="Q5" s="44">
+      <c r="Q5" s="35">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="R5" s="117">
+      <c r="R5" s="77">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="S5" s="44">
+      <c r="S5" s="35">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="T5" s="44">
+      <c r="T5" s="35">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="U5" s="44">
+      <c r="U5" s="35">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="V5" s="44">
+      <c r="V5" s="35">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="W5" s="44">
+      <c r="W5" s="35">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="X5" s="44">
+      <c r="X5" s="35">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="Y5" s="117">
+      <c r="Y5" s="77">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="Z5" s="44">
+      <c r="Z5" s="35">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="AA5" s="44">
+      <c r="AA5" s="35">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="AB5" s="44">
+      <c r="AB5" s="35">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="AC5" s="44">
+      <c r="AC5" s="35">
         <f>COUNTIFS(AC10:AC18,"休")</f>
         <v>0</v>
       </c>
-      <c r="AD5" s="44">
+      <c r="AD5" s="35">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="AE5" s="44">
+      <c r="AE5" s="35">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="AF5" s="117">
+      <c r="AF5" s="77">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="AG5" s="44">
+      <c r="AG5" s="35">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="AH5" s="44">
+      <c r="AH5" s="35">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="AI5" s="57"/>
-      <c r="AM5" s="45"/>
+      <c r="AI5" s="48"/>
+      <c r="AM5" s="36"/>
     </row>
     <row r="6" spans="1:44" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="C6" s="43" t="s">
+      <c r="C6" s="34" t="s">
         <v>3</v>
       </c>
-      <c r="D6" s="114">
+      <c r="D6" s="75">
         <f t="shared" ref="D6:AH6" si="1">COUNTIFS(D10:D18,"休")+COUNTIFS(D10:D18,"有")+COUNTIFS(D10:D18,"健")</f>
         <v>0</v>
       </c>
-      <c r="E6" s="44">
+      <c r="E6" s="35">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="F6" s="44">
+      <c r="F6" s="35">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="G6" s="44">
+      <c r="G6" s="35">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="H6" s="64">
+      <c r="H6" s="51">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="I6" s="44">
+      <c r="I6" s="35">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="J6" s="44">
+      <c r="J6" s="35">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="K6" s="44">
+      <c r="K6" s="35">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="L6" s="44">
+      <c r="L6" s="35">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="M6" s="44">
+      <c r="M6" s="35">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="N6" s="44">
+      <c r="N6" s="35">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="O6" s="44">
+      <c r="O6" s="35">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="P6" s="44">
+      <c r="P6" s="35">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="Q6" s="44">
+      <c r="Q6" s="35">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="R6" s="44">
+      <c r="R6" s="35">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="S6" s="44">
+      <c r="S6" s="35">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="T6" s="44">
+      <c r="T6" s="35">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="U6" s="44">
+      <c r="U6" s="35">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="V6" s="44">
+      <c r="V6" s="35">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="W6" s="44">
+      <c r="W6" s="35">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="X6" s="44">
+      <c r="X6" s="35">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="Y6" s="44">
+      <c r="Y6" s="35">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="Z6" s="44">
+      <c r="Z6" s="35">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="AA6" s="44">
+      <c r="AA6" s="35">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="AB6" s="44">
+      <c r="AB6" s="35">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="AC6" s="44">
+      <c r="AC6" s="35">
         <f>COUNTIFS(AC10:AC18,"休")+COUNTIFS(AC10:AC18,"有")+COUNTIFS(AC10:AC18,"健")</f>
         <v>0</v>
       </c>
-      <c r="AD6" s="44">
+      <c r="AD6" s="35">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="AE6" s="44">
+      <c r="AE6" s="35">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="AF6" s="44">
+      <c r="AF6" s="35">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="AG6" s="44">
+      <c r="AG6" s="35">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="AH6" s="44">
+      <c r="AH6" s="35">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="AI6" s="43"/>
+      <c r="AI6" s="34"/>
     </row>
     <row r="7" spans="1:44" ht="14.25" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="C7" s="13">
+      <c r="C7" s="12">
         <v>46296</v>
       </c>
-      <c r="D7" s="58">
+      <c r="D7" s="49">
         <v>1</v>
       </c>
-      <c r="E7" s="86">
+      <c r="E7" s="63">
         <f t="shared" ref="E7:T8" si="2">D7+1</f>
         <v>2</v>
       </c>
-      <c r="F7" s="53">
+      <c r="F7" s="44">
         <f t="shared" si="2"/>
         <v>3</v>
       </c>
-      <c r="G7" s="53">
+      <c r="G7" s="44">
         <f t="shared" si="2"/>
         <v>4</v>
       </c>
-      <c r="H7" s="53">
+      <c r="H7" s="44">
         <f t="shared" si="2"/>
         <v>5</v>
       </c>
-      <c r="I7" s="53">
+      <c r="I7" s="44">
         <f t="shared" si="2"/>
         <v>6</v>
       </c>
-      <c r="J7" s="53">
+      <c r="J7" s="44">
         <f t="shared" si="2"/>
         <v>7</v>
       </c>
-      <c r="K7" s="53">
+      <c r="K7" s="44">
         <f t="shared" si="2"/>
         <v>8</v>
       </c>
-      <c r="L7" s="86">
+      <c r="L7" s="63">
         <f t="shared" si="2"/>
         <v>9</v>
       </c>
-      <c r="M7" s="53">
+      <c r="M7" s="44">
         <f t="shared" si="2"/>
         <v>10</v>
       </c>
-      <c r="N7" s="53">
+      <c r="N7" s="44">
         <f t="shared" si="2"/>
         <v>11</v>
       </c>
-      <c r="O7" s="53">
+      <c r="O7" s="44">
         <f t="shared" si="2"/>
         <v>12</v>
       </c>
-      <c r="P7" s="53">
+      <c r="P7" s="44">
         <f t="shared" si="2"/>
         <v>13</v>
       </c>
-      <c r="Q7" s="53">
+      <c r="Q7" s="44">
         <f t="shared" si="2"/>
         <v>14</v>
       </c>
-      <c r="R7" s="53">
+      <c r="R7" s="44">
         <f t="shared" si="2"/>
         <v>15</v>
       </c>
-      <c r="S7" s="86">
+      <c r="S7" s="63">
         <f t="shared" si="2"/>
         <v>16</v>
       </c>
-      <c r="T7" s="53">
+      <c r="T7" s="44">
         <f t="shared" si="2"/>
         <v>17</v>
       </c>
-      <c r="U7" s="53">
+      <c r="U7" s="44">
         <f t="shared" ref="U7:AH8" si="3">T7+1</f>
         <v>18</v>
       </c>
-      <c r="V7" s="53">
+      <c r="V7" s="44">
         <f t="shared" si="3"/>
         <v>19</v>
       </c>
-      <c r="W7" s="53">
+      <c r="W7" s="44">
         <f t="shared" si="3"/>
         <v>20</v>
       </c>
-      <c r="X7" s="53">
+      <c r="X7" s="44">
         <f t="shared" si="3"/>
         <v>21</v>
       </c>
-      <c r="Y7" s="53">
+      <c r="Y7" s="44">
         <f t="shared" si="3"/>
         <v>22</v>
       </c>
-      <c r="Z7" s="86">
+      <c r="Z7" s="63">
         <f t="shared" si="3"/>
         <v>23</v>
       </c>
-      <c r="AA7" s="53">
+      <c r="AA7" s="44">
         <f t="shared" si="3"/>
         <v>24</v>
       </c>
-      <c r="AB7" s="53">
+      <c r="AB7" s="44">
         <f t="shared" si="3"/>
         <v>25</v>
       </c>
-      <c r="AC7" s="53">
+      <c r="AC7" s="44">
         <f t="shared" si="3"/>
         <v>26</v>
       </c>
-      <c r="AD7" s="53">
+      <c r="AD7" s="44">
         <f t="shared" si="3"/>
         <v>27</v>
       </c>
-      <c r="AE7" s="53">
+      <c r="AE7" s="44">
         <f t="shared" si="3"/>
         <v>28</v>
       </c>
-      <c r="AF7" s="53">
+      <c r="AF7" s="44">
         <f t="shared" si="3"/>
         <v>29</v>
       </c>
-      <c r="AG7" s="86">
+      <c r="AG7" s="63">
         <f t="shared" si="3"/>
         <v>30</v>
       </c>
-      <c r="AH7" s="53">
+      <c r="AH7" s="44">
         <f t="shared" si="3"/>
         <v>31</v>
       </c>
-      <c r="AI7" s="13"/>
+      <c r="AI7" s="12"/>
     </row>
     <row r="8" spans="1:44" customFormat="1" ht="14.1" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="C8" s="51" t="s">
-        <v>0</v>
-      </c>
-      <c r="D8" s="59">
+      <c r="C8" s="42" t="s">
+        <v>0</v>
+      </c>
+      <c r="D8" s="50">
         <f>C7</f>
         <v>46296</v>
       </c>
-      <c r="E8" s="54">
+      <c r="E8" s="45">
         <f t="shared" si="2"/>
         <v>46297</v>
       </c>
-      <c r="F8" s="54">
+      <c r="F8" s="45">
         <f t="shared" si="2"/>
         <v>46298</v>
       </c>
-      <c r="G8" s="56">
+      <c r="G8" s="47">
         <f t="shared" si="2"/>
         <v>46299</v>
       </c>
-      <c r="H8" s="54">
+      <c r="H8" s="45">
         <f t="shared" si="2"/>
         <v>46300</v>
       </c>
-      <c r="I8" s="54">
+      <c r="I8" s="45">
         <f t="shared" si="2"/>
         <v>46301</v>
       </c>
-      <c r="J8" s="54">
+      <c r="J8" s="45">
         <f t="shared" si="2"/>
         <v>46302</v>
       </c>
-      <c r="K8" s="54">
+      <c r="K8" s="45">
         <f t="shared" si="2"/>
         <v>46303</v>
       </c>
-      <c r="L8" s="54">
+      <c r="L8" s="45">
         <f t="shared" si="2"/>
         <v>46304</v>
       </c>
-      <c r="M8" s="54">
+      <c r="M8" s="45">
         <f t="shared" si="2"/>
         <v>46305</v>
       </c>
-      <c r="N8" s="54">
+      <c r="N8" s="45">
         <f t="shared" si="2"/>
         <v>46306</v>
       </c>
-      <c r="O8" s="54">
+      <c r="O8" s="45">
         <f t="shared" si="2"/>
         <v>46307</v>
       </c>
-      <c r="P8" s="54">
+      <c r="P8" s="45">
         <f t="shared" si="2"/>
         <v>46308</v>
       </c>
-      <c r="Q8" s="54">
+      <c r="Q8" s="45">
         <f t="shared" si="2"/>
         <v>46309</v>
       </c>
-      <c r="R8" s="54">
+      <c r="R8" s="45">
         <f t="shared" si="2"/>
         <v>46310</v>
       </c>
-      <c r="S8" s="54">
+      <c r="S8" s="45">
         <f t="shared" si="2"/>
         <v>46311</v>
       </c>
-      <c r="T8" s="54">
+      <c r="T8" s="45">
         <f t="shared" si="2"/>
         <v>46312</v>
       </c>
-      <c r="U8" s="54">
+      <c r="U8" s="45">
         <f t="shared" si="3"/>
         <v>46313</v>
       </c>
-      <c r="V8" s="54">
+      <c r="V8" s="45">
         <f t="shared" si="3"/>
         <v>46314</v>
       </c>
-      <c r="W8" s="54">
+      <c r="W8" s="45">
         <f t="shared" si="3"/>
         <v>46315</v>
       </c>
-      <c r="X8" s="54">
+      <c r="X8" s="45">
         <f t="shared" si="3"/>
         <v>46316</v>
       </c>
-      <c r="Y8" s="54">
+      <c r="Y8" s="45">
         <f t="shared" si="3"/>
         <v>46317</v>
       </c>
-      <c r="Z8" s="54">
+      <c r="Z8" s="45">
         <f t="shared" si="3"/>
         <v>46318</v>
       </c>
-      <c r="AA8" s="54">
+      <c r="AA8" s="45">
         <f t="shared" si="3"/>
         <v>46319</v>
       </c>
-      <c r="AB8" s="54">
+      <c r="AB8" s="45">
         <f t="shared" si="3"/>
         <v>46320</v>
       </c>
-      <c r="AC8" s="54">
+      <c r="AC8" s="45">
         <f t="shared" si="3"/>
         <v>46321</v>
       </c>
-      <c r="AD8" s="55">
+      <c r="AD8" s="46">
         <f t="shared" si="3"/>
         <v>46322</v>
       </c>
-      <c r="AE8" s="56">
+      <c r="AE8" s="47">
         <f t="shared" si="3"/>
         <v>46323</v>
       </c>
-      <c r="AF8" s="56">
+      <c r="AF8" s="47">
         <f t="shared" si="3"/>
         <v>46324</v>
       </c>
-      <c r="AG8" s="54">
+      <c r="AG8" s="45">
         <f t="shared" si="3"/>
         <v>46325</v>
       </c>
-      <c r="AH8" s="56">
+      <c r="AH8" s="47">
         <f t="shared" si="3"/>
         <v>46326</v>
       </c>
-      <c r="AI8" s="51" t="s">
+      <c r="AI8" s="42" t="s">
         <v>0</v>
       </c>
     </row>
@@ -5110,85 +4895,85 @@
       <c r="C9" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="D9" s="19"/>
-      <c r="E9" s="87"/>
-      <c r="F9" s="41"/>
-      <c r="G9" s="42"/>
-      <c r="H9" s="65"/>
-      <c r="I9" s="40"/>
-      <c r="J9" s="40"/>
-      <c r="K9" s="41"/>
-      <c r="L9" s="87"/>
-      <c r="M9" s="41"/>
-      <c r="N9" s="41"/>
-      <c r="O9" s="40"/>
-      <c r="P9" s="40"/>
-      <c r="Q9" s="41"/>
-      <c r="R9" s="41"/>
-      <c r="S9" s="87"/>
-      <c r="T9" s="40"/>
-      <c r="U9" s="40"/>
-      <c r="V9" s="40"/>
-      <c r="W9" s="41"/>
-      <c r="X9" s="41"/>
-      <c r="Y9" s="41"/>
-      <c r="Z9" s="103"/>
-      <c r="AA9" s="40"/>
-      <c r="AB9" s="40"/>
-      <c r="AC9" s="41"/>
-      <c r="AD9" s="41"/>
-      <c r="AE9" s="41"/>
-      <c r="AF9" s="40"/>
-      <c r="AG9" s="104"/>
-      <c r="AH9" s="39"/>
+      <c r="D9" s="16"/>
+      <c r="E9" s="64"/>
+      <c r="F9" s="32"/>
+      <c r="G9" s="33"/>
+      <c r="H9" s="52"/>
+      <c r="I9" s="31"/>
+      <c r="J9" s="31"/>
+      <c r="K9" s="32"/>
+      <c r="L9" s="64"/>
+      <c r="M9" s="32"/>
+      <c r="N9" s="32"/>
+      <c r="O9" s="31"/>
+      <c r="P9" s="31"/>
+      <c r="Q9" s="32"/>
+      <c r="R9" s="32"/>
+      <c r="S9" s="64"/>
+      <c r="T9" s="31"/>
+      <c r="U9" s="31"/>
+      <c r="V9" s="31"/>
+      <c r="W9" s="32"/>
+      <c r="X9" s="32"/>
+      <c r="Y9" s="32"/>
+      <c r="Z9" s="68"/>
+      <c r="AA9" s="31"/>
+      <c r="AB9" s="31"/>
+      <c r="AC9" s="32"/>
+      <c r="AD9" s="32"/>
+      <c r="AE9" s="32"/>
+      <c r="AF9" s="31"/>
+      <c r="AG9" s="69"/>
+      <c r="AH9" s="30"/>
       <c r="AI9" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="AJ9" s="38" t="s">
+      <c r="AJ9" s="29" t="s">
         <v>2</v>
       </c>
-      <c r="AK9" s="38"/>
+      <c r="AK9" s="29"/>
     </row>
     <row r="10" spans="1:44" ht="21.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A10" s="1">
         <v>1</v>
       </c>
-      <c r="B10" s="139"/>
-      <c r="C10" s="9" t="s">
+      <c r="B10" s="81"/>
+      <c r="C10" s="8" t="s">
         <v>5</v>
       </c>
-      <c r="D10" s="29"/>
-      <c r="E10" s="77"/>
-      <c r="F10" s="11"/>
-      <c r="G10" s="70"/>
-      <c r="H10" s="70"/>
-      <c r="I10" s="11"/>
-      <c r="J10" s="11"/>
-      <c r="K10" s="11"/>
-      <c r="L10" s="96"/>
-      <c r="M10" s="11"/>
-      <c r="N10" s="11"/>
-      <c r="O10" s="11"/>
-      <c r="P10" s="11"/>
-      <c r="Q10" s="11"/>
-      <c r="R10" s="11"/>
-      <c r="S10" s="96"/>
-      <c r="T10" s="70"/>
-      <c r="U10" s="70"/>
-      <c r="V10" s="108"/>
-      <c r="W10" s="11"/>
-      <c r="X10" s="11"/>
-      <c r="Y10" s="11"/>
-      <c r="Z10" s="77"/>
-      <c r="AA10" s="37"/>
-      <c r="AB10" s="11"/>
-      <c r="AC10" s="81"/>
-      <c r="AD10" s="11"/>
-      <c r="AE10" s="11"/>
-      <c r="AF10" s="11"/>
-      <c r="AG10" s="77"/>
-      <c r="AH10" s="60"/>
-      <c r="AI10" s="9" t="s">
+      <c r="D10" s="22"/>
+      <c r="E10" s="59"/>
+      <c r="F10" s="10"/>
+      <c r="G10" s="10"/>
+      <c r="H10" s="10"/>
+      <c r="I10" s="10"/>
+      <c r="J10" s="10"/>
+      <c r="K10" s="10"/>
+      <c r="L10" s="59"/>
+      <c r="M10" s="10"/>
+      <c r="N10" s="10"/>
+      <c r="O10" s="10"/>
+      <c r="P10" s="10"/>
+      <c r="Q10" s="10"/>
+      <c r="R10" s="10"/>
+      <c r="S10" s="59"/>
+      <c r="T10" s="10"/>
+      <c r="U10" s="10"/>
+      <c r="V10" s="10"/>
+      <c r="W10" s="10"/>
+      <c r="X10" s="10"/>
+      <c r="Y10" s="10"/>
+      <c r="Z10" s="59"/>
+      <c r="AA10" s="28"/>
+      <c r="AB10" s="10"/>
+      <c r="AC10" s="10"/>
+      <c r="AD10" s="10"/>
+      <c r="AE10" s="10"/>
+      <c r="AF10" s="10"/>
+      <c r="AG10" s="59"/>
+      <c r="AH10" s="14"/>
+      <c r="AI10" s="8" t="s">
         <v>5</v>
       </c>
       <c r="AJ10" s="2">
@@ -5196,51 +4981,51 @@
         <v>0</v>
       </c>
       <c r="AK10" s="2"/>
-      <c r="AL10" s="30" t="s">
+      <c r="AL10" s="23" t="s">
         <v>9</v>
       </c>
-      <c r="AM10" s="30"/>
+      <c r="AM10" s="23"/>
     </row>
     <row r="11" spans="1:44" ht="21.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A11" s="1">
         <v>2</v>
       </c>
-      <c r="B11" s="139"/>
-      <c r="C11" s="8" t="s">
+      <c r="B11" s="81"/>
+      <c r="C11" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="D11" s="7"/>
-      <c r="E11" s="88"/>
-      <c r="F11" s="6"/>
-      <c r="G11" s="6"/>
-      <c r="H11" s="11"/>
-      <c r="I11" s="79"/>
-      <c r="J11" s="6"/>
-      <c r="K11" s="6"/>
-      <c r="L11" s="88"/>
-      <c r="M11" s="6"/>
-      <c r="N11" s="6"/>
-      <c r="O11" s="79"/>
-      <c r="P11" s="6"/>
-      <c r="Q11" s="6"/>
-      <c r="R11" s="6"/>
-      <c r="S11" s="88"/>
-      <c r="T11" s="6"/>
-      <c r="U11" s="6"/>
-      <c r="V11" s="79"/>
-      <c r="W11" s="6"/>
-      <c r="X11" s="6"/>
-      <c r="Y11" s="6"/>
-      <c r="Z11" s="88"/>
-      <c r="AA11" s="6"/>
-      <c r="AB11" s="6"/>
-      <c r="AC11" s="81"/>
-      <c r="AD11" s="70"/>
-      <c r="AE11" s="11"/>
-      <c r="AF11" s="11"/>
-      <c r="AG11" s="88"/>
-      <c r="AH11" s="61"/>
-      <c r="AI11" s="8" t="s">
+      <c r="D11" s="6"/>
+      <c r="E11" s="65"/>
+      <c r="F11" s="5"/>
+      <c r="G11" s="5"/>
+      <c r="H11" s="10"/>
+      <c r="I11" s="5"/>
+      <c r="J11" s="5"/>
+      <c r="K11" s="5"/>
+      <c r="L11" s="65"/>
+      <c r="M11" s="5"/>
+      <c r="N11" s="5"/>
+      <c r="O11" s="5"/>
+      <c r="P11" s="5"/>
+      <c r="Q11" s="5"/>
+      <c r="R11" s="5"/>
+      <c r="S11" s="65"/>
+      <c r="T11" s="5"/>
+      <c r="U11" s="5"/>
+      <c r="V11" s="5"/>
+      <c r="W11" s="5"/>
+      <c r="X11" s="5"/>
+      <c r="Y11" s="5"/>
+      <c r="Z11" s="65"/>
+      <c r="AA11" s="5"/>
+      <c r="AB11" s="5"/>
+      <c r="AC11" s="10"/>
+      <c r="AD11" s="10"/>
+      <c r="AE11" s="10"/>
+      <c r="AF11" s="10"/>
+      <c r="AG11" s="65"/>
+      <c r="AH11" s="5"/>
+      <c r="AI11" s="7" t="s">
         <v>6</v>
       </c>
       <c r="AJ11" s="2">
@@ -5248,51 +5033,51 @@
         <v>0</v>
       </c>
       <c r="AK11" s="2"/>
-      <c r="AL11" s="30" t="s">
+      <c r="AL11" s="23" t="s">
         <v>9</v>
       </c>
-      <c r="AM11" s="30"/>
+      <c r="AM11" s="23"/>
     </row>
     <row r="12" spans="1:44" ht="21.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A12" s="1">
         <v>3</v>
       </c>
-      <c r="B12" s="52"/>
-      <c r="C12" s="36" t="s">
+      <c r="B12" s="43"/>
+      <c r="C12" s="27" t="s">
         <v>11</v>
       </c>
-      <c r="D12" s="29"/>
-      <c r="E12" s="89"/>
-      <c r="F12" s="75"/>
-      <c r="G12" s="18"/>
-      <c r="H12" s="18"/>
-      <c r="I12" s="18"/>
-      <c r="J12" s="18"/>
-      <c r="K12" s="118"/>
-      <c r="L12" s="97"/>
-      <c r="M12" s="15"/>
-      <c r="N12" s="15"/>
-      <c r="O12" s="15"/>
-      <c r="P12" s="15"/>
-      <c r="Q12" s="15"/>
-      <c r="R12" s="15"/>
-      <c r="S12" s="97"/>
-      <c r="T12" s="18"/>
-      <c r="U12" s="15"/>
-      <c r="V12" s="15"/>
-      <c r="W12" s="15"/>
-      <c r="X12" s="18"/>
-      <c r="Y12" s="15"/>
-      <c r="Z12" s="89"/>
-      <c r="AA12" s="15"/>
-      <c r="AB12" s="18"/>
-      <c r="AC12" s="82"/>
-      <c r="AD12" s="18"/>
-      <c r="AE12" s="18"/>
-      <c r="AF12" s="18"/>
-      <c r="AG12" s="109"/>
-      <c r="AH12" s="62"/>
-      <c r="AI12" s="36" t="s">
+      <c r="D12" s="22"/>
+      <c r="E12" s="66"/>
+      <c r="F12" s="14"/>
+      <c r="G12" s="15"/>
+      <c r="H12" s="15"/>
+      <c r="I12" s="15"/>
+      <c r="J12" s="15"/>
+      <c r="K12" s="15"/>
+      <c r="L12" s="67"/>
+      <c r="M12" s="14"/>
+      <c r="N12" s="14"/>
+      <c r="O12" s="14"/>
+      <c r="P12" s="14"/>
+      <c r="Q12" s="14"/>
+      <c r="R12" s="14"/>
+      <c r="S12" s="67"/>
+      <c r="T12" s="15"/>
+      <c r="U12" s="14"/>
+      <c r="V12" s="14"/>
+      <c r="W12" s="14"/>
+      <c r="X12" s="15"/>
+      <c r="Y12" s="14"/>
+      <c r="Z12" s="66"/>
+      <c r="AA12" s="14"/>
+      <c r="AB12" s="15"/>
+      <c r="AC12" s="15"/>
+      <c r="AD12" s="15"/>
+      <c r="AE12" s="15"/>
+      <c r="AF12" s="15"/>
+      <c r="AG12" s="67"/>
+      <c r="AH12" s="15"/>
+      <c r="AI12" s="27" t="s">
         <v>11</v>
       </c>
       <c r="AJ12" s="2">
@@ -5300,7 +5085,7 @@
         <v>0</v>
       </c>
       <c r="AK12" s="2"/>
-      <c r="AL12" s="30" t="s">
+      <c r="AL12" s="23" t="s">
         <v>12</v>
       </c>
     </row>
@@ -5308,42 +5093,42 @@
       <c r="A13" s="1">
         <v>4</v>
       </c>
-      <c r="B13" s="52"/>
-      <c r="C13" s="24" t="s">
+      <c r="B13" s="43"/>
+      <c r="C13" s="20" t="s">
         <v>13</v>
       </c>
-      <c r="D13" s="29"/>
-      <c r="E13" s="89"/>
-      <c r="F13" s="15"/>
-      <c r="G13" s="15"/>
-      <c r="H13" s="11"/>
-      <c r="I13" s="81"/>
-      <c r="J13" s="15"/>
-      <c r="K13" s="15"/>
-      <c r="L13" s="110"/>
-      <c r="M13" s="50"/>
-      <c r="N13" s="60"/>
-      <c r="O13" s="75"/>
-      <c r="P13" s="15"/>
-      <c r="Q13" s="121"/>
-      <c r="R13" s="15"/>
-      <c r="S13" s="89"/>
-      <c r="T13" s="15"/>
-      <c r="U13" s="15"/>
-      <c r="V13" s="15"/>
-      <c r="W13" s="15"/>
-      <c r="X13" s="15"/>
-      <c r="Y13" s="15"/>
-      <c r="Z13" s="77"/>
-      <c r="AA13" s="81"/>
-      <c r="AB13" s="11"/>
-      <c r="AC13" s="15"/>
-      <c r="AD13" s="80"/>
-      <c r="AE13" s="15"/>
-      <c r="AF13" s="15"/>
-      <c r="AG13" s="89"/>
-      <c r="AH13" s="60"/>
-      <c r="AI13" s="24" t="s">
+      <c r="D13" s="22"/>
+      <c r="E13" s="66"/>
+      <c r="F13" s="14"/>
+      <c r="G13" s="14"/>
+      <c r="H13" s="10"/>
+      <c r="I13" s="10"/>
+      <c r="J13" s="14"/>
+      <c r="K13" s="14"/>
+      <c r="L13" s="71"/>
+      <c r="M13" s="41"/>
+      <c r="N13" s="14"/>
+      <c r="O13" s="14"/>
+      <c r="P13" s="14"/>
+      <c r="Q13" s="80"/>
+      <c r="R13" s="14"/>
+      <c r="S13" s="66"/>
+      <c r="T13" s="14"/>
+      <c r="U13" s="14"/>
+      <c r="V13" s="14"/>
+      <c r="W13" s="14"/>
+      <c r="X13" s="14"/>
+      <c r="Y13" s="14"/>
+      <c r="Z13" s="59"/>
+      <c r="AA13" s="10"/>
+      <c r="AB13" s="10"/>
+      <c r="AC13" s="14"/>
+      <c r="AD13" s="14"/>
+      <c r="AE13" s="14"/>
+      <c r="AF13" s="14"/>
+      <c r="AG13" s="66"/>
+      <c r="AH13" s="14"/>
+      <c r="AI13" s="20" t="s">
         <v>13</v>
       </c>
       <c r="AJ13" s="2">
@@ -5351,7 +5136,7 @@
         <v>0</v>
       </c>
       <c r="AK13" s="2"/>
-      <c r="AL13" s="30" t="s">
+      <c r="AL13" s="23" t="s">
         <v>14</v>
       </c>
     </row>
@@ -5359,40 +5144,40 @@
       <c r="A14" s="1">
         <v>5</v>
       </c>
-      <c r="B14" s="52"/>
-      <c r="C14" s="8"/>
-      <c r="D14" s="7"/>
-      <c r="E14" s="88"/>
-      <c r="F14" s="6"/>
-      <c r="G14" s="6"/>
-      <c r="H14" s="6"/>
-      <c r="I14" s="6"/>
-      <c r="J14" s="6"/>
-      <c r="K14" s="6"/>
-      <c r="L14" s="88"/>
-      <c r="M14" s="6"/>
-      <c r="N14" s="6"/>
-      <c r="O14" s="6"/>
-      <c r="P14" s="6"/>
-      <c r="Q14" s="6"/>
-      <c r="R14" s="6"/>
-      <c r="S14" s="88"/>
-      <c r="T14" s="6"/>
-      <c r="U14" s="6"/>
-      <c r="V14" s="6"/>
-      <c r="W14" s="6"/>
-      <c r="X14" s="6"/>
-      <c r="Y14" s="6"/>
-      <c r="Z14" s="88"/>
-      <c r="AA14" s="6"/>
-      <c r="AB14" s="6"/>
-      <c r="AC14" s="6"/>
-      <c r="AD14" s="6"/>
-      <c r="AE14" s="6"/>
-      <c r="AF14" s="6"/>
-      <c r="AG14" s="105"/>
-      <c r="AH14" s="63"/>
-      <c r="AI14" s="8"/>
+      <c r="B14" s="43"/>
+      <c r="C14" s="7"/>
+      <c r="D14" s="6"/>
+      <c r="E14" s="65"/>
+      <c r="F14" s="5"/>
+      <c r="G14" s="5"/>
+      <c r="H14" s="5"/>
+      <c r="I14" s="5"/>
+      <c r="J14" s="5"/>
+      <c r="K14" s="5"/>
+      <c r="L14" s="65"/>
+      <c r="M14" s="5"/>
+      <c r="N14" s="5"/>
+      <c r="O14" s="5"/>
+      <c r="P14" s="5"/>
+      <c r="Q14" s="5"/>
+      <c r="R14" s="5"/>
+      <c r="S14" s="65"/>
+      <c r="T14" s="5"/>
+      <c r="U14" s="5"/>
+      <c r="V14" s="5"/>
+      <c r="W14" s="5"/>
+      <c r="X14" s="5"/>
+      <c r="Y14" s="5"/>
+      <c r="Z14" s="65"/>
+      <c r="AA14" s="5"/>
+      <c r="AB14" s="5"/>
+      <c r="AC14" s="5"/>
+      <c r="AD14" s="5"/>
+      <c r="AE14" s="5"/>
+      <c r="AF14" s="5"/>
+      <c r="AG14" s="65"/>
+      <c r="AH14" s="104"/>
+      <c r="AI14" s="7"/>
       <c r="AJ14" s="2">
         <f t="shared" si="4"/>
         <v>0</v>
@@ -5406,42 +5191,42 @@
       <c r="A15" s="1">
         <v>6</v>
       </c>
-      <c r="B15" s="35"/>
-      <c r="C15" s="36" t="s">
+      <c r="B15" s="26"/>
+      <c r="C15" s="27" t="s">
         <v>8</v>
       </c>
-      <c r="D15" s="115"/>
-      <c r="E15" s="89"/>
-      <c r="F15" s="15"/>
-      <c r="G15" s="15"/>
-      <c r="H15" s="15"/>
-      <c r="I15" s="15"/>
-      <c r="J15" s="15"/>
-      <c r="K15" s="15"/>
-      <c r="L15" s="89"/>
-      <c r="M15" s="15"/>
-      <c r="N15" s="15"/>
-      <c r="O15" s="75"/>
-      <c r="P15" s="15"/>
-      <c r="Q15" s="15"/>
-      <c r="R15" s="15"/>
-      <c r="S15" s="89"/>
-      <c r="T15" s="15"/>
-      <c r="U15" s="75"/>
-      <c r="V15" s="15"/>
-      <c r="W15" s="75"/>
-      <c r="X15" s="15"/>
-      <c r="Y15" s="15"/>
-      <c r="Z15" s="89"/>
-      <c r="AA15" s="15"/>
-      <c r="AB15" s="15"/>
-      <c r="AC15" s="15"/>
-      <c r="AD15" s="15"/>
-      <c r="AE15" s="15"/>
-      <c r="AF15" s="15"/>
-      <c r="AG15" s="89"/>
-      <c r="AH15" s="84"/>
-      <c r="AI15" s="85" t="s">
+      <c r="D15" s="22"/>
+      <c r="E15" s="66"/>
+      <c r="F15" s="14"/>
+      <c r="G15" s="14"/>
+      <c r="H15" s="14"/>
+      <c r="I15" s="14"/>
+      <c r="J15" s="14"/>
+      <c r="K15" s="14"/>
+      <c r="L15" s="66"/>
+      <c r="M15" s="14"/>
+      <c r="N15" s="14"/>
+      <c r="O15" s="14"/>
+      <c r="P15" s="14"/>
+      <c r="Q15" s="14"/>
+      <c r="R15" s="14"/>
+      <c r="S15" s="66"/>
+      <c r="T15" s="14"/>
+      <c r="U15" s="14"/>
+      <c r="V15" s="14"/>
+      <c r="W15" s="14"/>
+      <c r="X15" s="14"/>
+      <c r="Y15" s="14"/>
+      <c r="Z15" s="66"/>
+      <c r="AA15" s="14"/>
+      <c r="AB15" s="14"/>
+      <c r="AC15" s="14"/>
+      <c r="AD15" s="14"/>
+      <c r="AE15" s="14"/>
+      <c r="AF15" s="14"/>
+      <c r="AG15" s="66"/>
+      <c r="AH15" s="105"/>
+      <c r="AI15" s="62" t="s">
         <v>8</v>
       </c>
       <c r="AJ15" s="2">
@@ -5449,7 +5234,7 @@
         <v>0</v>
       </c>
       <c r="AK15" s="2"/>
-      <c r="AL15" s="30" t="s">
+      <c r="AL15" s="23" t="s">
         <v>19</v>
       </c>
     </row>
@@ -5457,42 +5242,42 @@
       <c r="A16" s="1">
         <v>7</v>
       </c>
-      <c r="B16" s="35"/>
-      <c r="C16" s="10" t="s">
+      <c r="B16" s="26"/>
+      <c r="C16" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="D16" s="29"/>
-      <c r="E16" s="89"/>
-      <c r="F16" s="70"/>
-      <c r="G16" s="70"/>
-      <c r="H16" s="70"/>
-      <c r="I16" s="11"/>
-      <c r="J16" s="15"/>
-      <c r="K16" s="15"/>
-      <c r="L16" s="96"/>
-      <c r="M16" s="75"/>
-      <c r="N16" s="75"/>
-      <c r="O16" s="75"/>
-      <c r="P16" s="15"/>
-      <c r="Q16" s="15"/>
-      <c r="R16" s="11"/>
-      <c r="S16" s="89"/>
-      <c r="T16" s="15"/>
-      <c r="U16" s="11"/>
-      <c r="V16" s="15"/>
-      <c r="W16" s="15"/>
-      <c r="X16" s="15"/>
-      <c r="Y16" s="15"/>
-      <c r="Z16" s="89"/>
-      <c r="AA16" s="11"/>
-      <c r="AB16" s="11"/>
-      <c r="AC16" s="15"/>
-      <c r="AD16" s="15"/>
-      <c r="AE16" s="15"/>
-      <c r="AF16" s="15"/>
-      <c r="AG16" s="77"/>
-      <c r="AH16" s="75"/>
-      <c r="AI16" s="10" t="s">
+      <c r="D16" s="22"/>
+      <c r="E16" s="66"/>
+      <c r="F16" s="10"/>
+      <c r="G16" s="10"/>
+      <c r="H16" s="10"/>
+      <c r="I16" s="10"/>
+      <c r="J16" s="14"/>
+      <c r="K16" s="14"/>
+      <c r="L16" s="59"/>
+      <c r="M16" s="14"/>
+      <c r="N16" s="14"/>
+      <c r="O16" s="14"/>
+      <c r="P16" s="14"/>
+      <c r="Q16" s="14"/>
+      <c r="R16" s="10"/>
+      <c r="S16" s="66"/>
+      <c r="T16" s="14"/>
+      <c r="U16" s="10"/>
+      <c r="V16" s="14"/>
+      <c r="W16" s="14"/>
+      <c r="X16" s="14"/>
+      <c r="Y16" s="14"/>
+      <c r="Z16" s="66"/>
+      <c r="AA16" s="10"/>
+      <c r="AB16" s="10"/>
+      <c r="AC16" s="14"/>
+      <c r="AD16" s="14"/>
+      <c r="AE16" s="14"/>
+      <c r="AF16" s="14"/>
+      <c r="AG16" s="59"/>
+      <c r="AH16" s="14"/>
+      <c r="AI16" s="9" t="s">
         <v>10</v>
       </c>
       <c r="AJ16" s="2">
@@ -5500,51 +5285,51 @@
         <v>0</v>
       </c>
       <c r="AK16" s="2"/>
-      <c r="AL16" s="140" t="s">
+      <c r="AL16" s="82" t="s">
         <v>17</v>
       </c>
-      <c r="AM16" s="140"/>
+      <c r="AM16" s="82"/>
     </row>
     <row r="17" spans="1:39" ht="21.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A17" s="1">
         <v>8</v>
       </c>
-      <c r="B17" s="35"/>
-      <c r="C17" s="9" t="s">
+      <c r="B17" s="26"/>
+      <c r="C17" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="D17" s="29"/>
-      <c r="E17" s="89"/>
-      <c r="F17" s="15"/>
-      <c r="G17" s="11"/>
-      <c r="H17" s="11"/>
-      <c r="I17" s="15"/>
-      <c r="J17" s="15"/>
-      <c r="K17" s="15"/>
-      <c r="L17" s="89"/>
-      <c r="M17" s="15"/>
-      <c r="N17" s="75"/>
-      <c r="O17" s="15"/>
-      <c r="P17" s="75"/>
-      <c r="Q17" s="75"/>
-      <c r="R17" s="15"/>
-      <c r="S17" s="89"/>
-      <c r="T17" s="15"/>
-      <c r="U17" s="15"/>
-      <c r="V17" s="11"/>
-      <c r="W17" s="11"/>
-      <c r="X17" s="15"/>
-      <c r="Y17" s="15"/>
-      <c r="Z17" s="89"/>
-      <c r="AA17" s="15"/>
-      <c r="AB17" s="15"/>
-      <c r="AC17" s="11"/>
-      <c r="AD17" s="15"/>
-      <c r="AE17" s="15"/>
-      <c r="AF17" s="15"/>
-      <c r="AG17" s="89"/>
-      <c r="AH17" s="32"/>
-      <c r="AI17" s="9" t="s">
+      <c r="D17" s="22"/>
+      <c r="E17" s="66"/>
+      <c r="F17" s="14"/>
+      <c r="G17" s="10"/>
+      <c r="H17" s="10"/>
+      <c r="I17" s="14"/>
+      <c r="J17" s="14"/>
+      <c r="K17" s="14"/>
+      <c r="L17" s="66"/>
+      <c r="M17" s="14"/>
+      <c r="N17" s="14"/>
+      <c r="O17" s="14"/>
+      <c r="P17" s="14"/>
+      <c r="Q17" s="14"/>
+      <c r="R17" s="14"/>
+      <c r="S17" s="66"/>
+      <c r="T17" s="14"/>
+      <c r="U17" s="14"/>
+      <c r="V17" s="10"/>
+      <c r="W17" s="10"/>
+      <c r="X17" s="14"/>
+      <c r="Y17" s="14"/>
+      <c r="Z17" s="66"/>
+      <c r="AA17" s="14"/>
+      <c r="AB17" s="14"/>
+      <c r="AC17" s="10"/>
+      <c r="AD17" s="14"/>
+      <c r="AE17" s="14"/>
+      <c r="AF17" s="14"/>
+      <c r="AG17" s="66"/>
+      <c r="AH17" s="10"/>
+      <c r="AI17" s="8" t="s">
         <v>18</v>
       </c>
       <c r="AJ17" s="2">
@@ -5552,261 +5337,261 @@
         <v>0</v>
       </c>
       <c r="AK17" s="2"/>
-      <c r="AL17" s="83" t="s">
+      <c r="AL17" s="61" t="s">
         <v>16</v>
       </c>
-      <c r="AM17" s="83"/>
+      <c r="AM17" s="61"/>
     </row>
     <row r="18" spans="1:39" ht="21.75" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B18" s="141"/>
-      <c r="C18" s="10"/>
-      <c r="D18" s="29"/>
-      <c r="E18" s="89"/>
-      <c r="F18" s="15"/>
-      <c r="G18" s="15"/>
-      <c r="H18" s="15"/>
-      <c r="I18" s="15"/>
-      <c r="J18" s="11"/>
-      <c r="K18" s="15"/>
-      <c r="L18" s="89"/>
-      <c r="M18" s="11"/>
-      <c r="N18" s="11"/>
-      <c r="O18" s="15"/>
-      <c r="P18" s="15"/>
-      <c r="Q18" s="15"/>
-      <c r="R18" s="15"/>
-      <c r="S18" s="102"/>
-      <c r="T18" s="11"/>
-      <c r="U18" s="76"/>
-      <c r="V18" s="34"/>
-      <c r="W18" s="34"/>
-      <c r="X18" s="15"/>
-      <c r="Y18" s="34"/>
-      <c r="Z18" s="89"/>
-      <c r="AA18" s="15"/>
-      <c r="AB18" s="15"/>
-      <c r="AC18" s="34"/>
-      <c r="AD18" s="11"/>
-      <c r="AE18" s="15"/>
-      <c r="AF18" s="15"/>
-      <c r="AG18" s="77"/>
-      <c r="AH18" s="60"/>
-      <c r="AI18" s="10"/>
+      <c r="B18" s="83"/>
+      <c r="C18" s="9"/>
+      <c r="D18" s="22"/>
+      <c r="E18" s="66"/>
+      <c r="F18" s="14"/>
+      <c r="G18" s="14"/>
+      <c r="H18" s="14"/>
+      <c r="I18" s="14"/>
+      <c r="J18" s="10"/>
+      <c r="K18" s="14"/>
+      <c r="L18" s="66"/>
+      <c r="M18" s="10"/>
+      <c r="N18" s="10"/>
+      <c r="O18" s="14"/>
+      <c r="P18" s="14"/>
+      <c r="Q18" s="14"/>
+      <c r="R18" s="14"/>
+      <c r="S18" s="66"/>
+      <c r="T18" s="10"/>
+      <c r="U18" s="10"/>
+      <c r="V18" s="14"/>
+      <c r="W18" s="14"/>
+      <c r="X18" s="14"/>
+      <c r="Y18" s="14"/>
+      <c r="Z18" s="66"/>
+      <c r="AA18" s="14"/>
+      <c r="AB18" s="14"/>
+      <c r="AC18" s="14"/>
+      <c r="AD18" s="10"/>
+      <c r="AE18" s="14"/>
+      <c r="AF18" s="14"/>
+      <c r="AG18" s="59"/>
+      <c r="AH18" s="14"/>
+      <c r="AI18" s="9"/>
       <c r="AJ18" s="2">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="AK18" s="2"/>
-      <c r="AL18" s="30"/>
+      <c r="AL18" s="23"/>
     </row>
     <row r="19" spans="1:39" ht="21.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A19"/>
-      <c r="B19" s="141"/>
-      <c r="C19" s="24"/>
-      <c r="D19" s="29"/>
-      <c r="E19" s="77"/>
-      <c r="F19" s="11"/>
-      <c r="G19" s="11"/>
-      <c r="H19" s="11"/>
-      <c r="I19" s="11"/>
-      <c r="J19" s="28"/>
-      <c r="K19" s="28"/>
-      <c r="L19" s="77"/>
-      <c r="M19" s="11"/>
-      <c r="N19" s="15"/>
-      <c r="O19" s="11"/>
-      <c r="P19" s="11"/>
-      <c r="Q19" s="11"/>
-      <c r="R19" s="28"/>
-      <c r="S19" s="89"/>
-      <c r="T19" s="11"/>
-      <c r="U19" s="11"/>
-      <c r="V19" s="11"/>
-      <c r="W19" s="28"/>
-      <c r="X19" s="28"/>
-      <c r="Y19" s="11"/>
-      <c r="Z19" s="77"/>
-      <c r="AA19" s="28"/>
-      <c r="AB19" s="11"/>
-      <c r="AC19" s="11"/>
-      <c r="AD19" s="15"/>
-      <c r="AE19" s="28"/>
-      <c r="AF19" s="11"/>
-      <c r="AG19" s="89"/>
-      <c r="AH19" s="27"/>
-      <c r="AI19" s="10"/>
+      <c r="B19" s="83"/>
+      <c r="C19" s="20"/>
+      <c r="D19" s="22"/>
+      <c r="E19" s="59"/>
+      <c r="F19" s="10"/>
+      <c r="G19" s="10"/>
+      <c r="H19" s="10"/>
+      <c r="I19" s="10"/>
+      <c r="J19" s="21"/>
+      <c r="K19" s="21"/>
+      <c r="L19" s="59"/>
+      <c r="M19" s="10"/>
+      <c r="N19" s="14"/>
+      <c r="O19" s="10"/>
+      <c r="P19" s="10"/>
+      <c r="Q19" s="10"/>
+      <c r="R19" s="21"/>
+      <c r="S19" s="66"/>
+      <c r="T19" s="10"/>
+      <c r="U19" s="10"/>
+      <c r="V19" s="10"/>
+      <c r="W19" s="21"/>
+      <c r="X19" s="21"/>
+      <c r="Y19" s="10"/>
+      <c r="Z19" s="59"/>
+      <c r="AA19" s="21"/>
+      <c r="AB19" s="10"/>
+      <c r="AC19" s="10"/>
+      <c r="AD19" s="14"/>
+      <c r="AE19" s="21"/>
+      <c r="AF19" s="10"/>
+      <c r="AG19" s="66"/>
+      <c r="AH19" s="10"/>
+      <c r="AI19" s="9"/>
     </row>
     <row r="20" spans="1:39" ht="21.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A20"/>
-      <c r="B20" s="141"/>
-      <c r="C20" s="9"/>
-      <c r="D20" s="116"/>
-      <c r="E20" s="77"/>
-      <c r="F20" s="11"/>
-      <c r="G20" s="11"/>
-      <c r="H20" s="11"/>
-      <c r="I20" s="11"/>
-      <c r="J20" s="11"/>
-      <c r="K20" s="11"/>
-      <c r="L20" s="77"/>
-      <c r="M20" s="11"/>
-      <c r="N20" s="33"/>
-      <c r="O20" s="11"/>
-      <c r="P20" s="11"/>
-      <c r="Q20" s="11"/>
-      <c r="R20" s="11"/>
-      <c r="S20" s="77"/>
-      <c r="T20" s="11"/>
-      <c r="U20" s="11"/>
-      <c r="V20" s="11"/>
-      <c r="W20" s="11"/>
-      <c r="X20" s="11"/>
-      <c r="Y20" s="11"/>
-      <c r="Z20" s="77"/>
-      <c r="AA20" s="11"/>
-      <c r="AB20" s="11"/>
-      <c r="AC20" s="11"/>
-      <c r="AD20" s="33"/>
-      <c r="AE20" s="11"/>
-      <c r="AF20" s="11"/>
-      <c r="AG20" s="77"/>
-      <c r="AH20" s="27"/>
-      <c r="AI20" s="9"/>
+      <c r="B20" s="83"/>
+      <c r="C20" s="8"/>
+      <c r="D20" s="76"/>
+      <c r="E20" s="59"/>
+      <c r="F20" s="10"/>
+      <c r="G20" s="10"/>
+      <c r="H20" s="10"/>
+      <c r="I20" s="10"/>
+      <c r="J20" s="10"/>
+      <c r="K20" s="10"/>
+      <c r="L20" s="59"/>
+      <c r="M20" s="10"/>
+      <c r="N20" s="25"/>
+      <c r="O20" s="10"/>
+      <c r="P20" s="10"/>
+      <c r="Q20" s="10"/>
+      <c r="R20" s="10"/>
+      <c r="S20" s="59"/>
+      <c r="T20" s="10"/>
+      <c r="U20" s="10"/>
+      <c r="V20" s="10"/>
+      <c r="W20" s="10"/>
+      <c r="X20" s="10"/>
+      <c r="Y20" s="10"/>
+      <c r="Z20" s="59"/>
+      <c r="AA20" s="10"/>
+      <c r="AB20" s="10"/>
+      <c r="AC20" s="10"/>
+      <c r="AD20" s="25"/>
+      <c r="AE20" s="10"/>
+      <c r="AF20" s="10"/>
+      <c r="AG20" s="59"/>
+      <c r="AH20" s="10"/>
+      <c r="AI20" s="8"/>
     </row>
     <row r="21" spans="1:39" ht="21.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A21"/>
-      <c r="B21" s="141"/>
-      <c r="C21" s="8"/>
-      <c r="D21" s="31"/>
-      <c r="E21" s="88"/>
-      <c r="F21" s="26"/>
-      <c r="G21" s="6"/>
-      <c r="H21" s="78"/>
-      <c r="I21" s="6"/>
-      <c r="J21" s="6"/>
-      <c r="K21" s="6"/>
-      <c r="L21" s="88"/>
-      <c r="M21" s="6"/>
-      <c r="N21" s="78"/>
-      <c r="O21" s="6"/>
-      <c r="P21" s="6"/>
-      <c r="Q21" s="6"/>
-      <c r="R21" s="6"/>
-      <c r="S21" s="88"/>
-      <c r="T21" s="6"/>
-      <c r="U21" s="6"/>
-      <c r="V21" s="6"/>
-      <c r="W21" s="6"/>
-      <c r="X21" s="6"/>
-      <c r="Y21" s="6"/>
-      <c r="Z21" s="88"/>
-      <c r="AA21" s="6"/>
-      <c r="AB21" s="6"/>
-      <c r="AC21" s="6"/>
-      <c r="AD21" s="78"/>
-      <c r="AE21" s="6"/>
-      <c r="AF21" s="6"/>
-      <c r="AG21" s="88"/>
-      <c r="AH21" s="25"/>
-      <c r="AI21" s="8"/>
+      <c r="B21" s="83"/>
+      <c r="C21" s="7"/>
+      <c r="D21" s="24"/>
+      <c r="E21" s="65"/>
+      <c r="F21" s="5"/>
+      <c r="G21" s="5"/>
+      <c r="H21" s="60"/>
+      <c r="I21" s="5"/>
+      <c r="J21" s="5"/>
+      <c r="K21" s="5"/>
+      <c r="L21" s="65"/>
+      <c r="M21" s="5"/>
+      <c r="N21" s="60"/>
+      <c r="O21" s="5"/>
+      <c r="P21" s="5"/>
+      <c r="Q21" s="5"/>
+      <c r="R21" s="5"/>
+      <c r="S21" s="65"/>
+      <c r="T21" s="5"/>
+      <c r="U21" s="5"/>
+      <c r="V21" s="5"/>
+      <c r="W21" s="5"/>
+      <c r="X21" s="5"/>
+      <c r="Y21" s="5"/>
+      <c r="Z21" s="65"/>
+      <c r="AA21" s="5"/>
+      <c r="AB21" s="5"/>
+      <c r="AC21" s="5"/>
+      <c r="AD21" s="60"/>
+      <c r="AE21" s="5"/>
+      <c r="AF21" s="5"/>
+      <c r="AG21" s="65"/>
+      <c r="AH21" s="106"/>
+      <c r="AI21" s="7"/>
     </row>
     <row r="22" spans="1:39" ht="12.75" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B22" s="22"/>
-      <c r="C22" s="13">
+      <c r="B22" s="19"/>
+      <c r="C22" s="12">
         <f>C7</f>
         <v>46296</v>
       </c>
-      <c r="D22" s="93">
+      <c r="D22" s="107">
         <v>1</v>
       </c>
-      <c r="E22" s="90">
+      <c r="E22" s="108">
         <v>2</v>
       </c>
-      <c r="F22" s="23">
+      <c r="F22" s="109">
         <v>3</v>
       </c>
-      <c r="G22" s="23">
+      <c r="G22" s="109">
         <v>4</v>
       </c>
-      <c r="H22" s="66">
+      <c r="H22" s="110">
         <v>5</v>
       </c>
-      <c r="I22" s="23">
+      <c r="I22" s="109">
         <v>6</v>
       </c>
-      <c r="J22" s="23">
+      <c r="J22" s="109">
         <v>7</v>
       </c>
-      <c r="K22" s="99">
+      <c r="K22" s="109">
         <v>8</v>
       </c>
-      <c r="L22" s="98">
+      <c r="L22" s="109">
         <v>9</v>
       </c>
-      <c r="M22" s="23">
+      <c r="M22" s="109">
         <v>10</v>
       </c>
-      <c r="N22" s="23">
+      <c r="N22" s="109">
         <v>11</v>
       </c>
-      <c r="O22" s="23">
+      <c r="O22" s="109">
         <v>12</v>
       </c>
-      <c r="P22" s="23">
+      <c r="P22" s="109">
         <v>13</v>
       </c>
-      <c r="Q22" s="23">
+      <c r="Q22" s="109">
         <v>14</v>
       </c>
-      <c r="R22" s="99">
+      <c r="R22" s="109">
         <v>15</v>
       </c>
-      <c r="S22" s="98">
+      <c r="S22" s="109">
         <v>16</v>
       </c>
-      <c r="T22" s="23">
+      <c r="T22" s="109">
         <v>17</v>
       </c>
-      <c r="U22" s="23">
+      <c r="U22" s="109">
         <v>18</v>
       </c>
-      <c r="V22" s="23">
+      <c r="V22" s="109">
         <v>19</v>
       </c>
-      <c r="W22" s="23">
+      <c r="W22" s="109">
         <v>20</v>
       </c>
-      <c r="X22" s="23">
+      <c r="X22" s="109">
         <v>21</v>
       </c>
-      <c r="Y22" s="99">
+      <c r="Y22" s="109">
         <v>22</v>
       </c>
-      <c r="Z22" s="98">
+      <c r="Z22" s="109">
         <v>23</v>
       </c>
-      <c r="AA22" s="23">
+      <c r="AA22" s="109">
         <v>24</v>
       </c>
-      <c r="AB22" s="23">
+      <c r="AB22" s="109">
         <v>25</v>
       </c>
-      <c r="AC22" s="23">
+      <c r="AC22" s="109">
         <v>26</v>
       </c>
-      <c r="AD22" s="23">
+      <c r="AD22" s="109">
         <v>27</v>
       </c>
-      <c r="AE22" s="23">
+      <c r="AE22" s="109">
         <v>28</v>
       </c>
-      <c r="AF22" s="99">
+      <c r="AF22" s="109">
         <v>29</v>
       </c>
-      <c r="AG22" s="90">
+      <c r="AG22" s="108">
         <v>30</v>
       </c>
-      <c r="AH22" s="5">
+      <c r="AH22" s="111">
         <f>AH7</f>
         <v>31</v>
       </c>
@@ -5820,135 +5605,135 @@
       </c>
     </row>
     <row r="23" spans="1:39" ht="11.25" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B23" s="22"/>
-      <c r="C23" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="D23" s="94">
+      <c r="B23" s="19"/>
+      <c r="C23" s="11" t="s">
+        <v>0</v>
+      </c>
+      <c r="D23" s="112">
         <f>C7</f>
         <v>46296</v>
       </c>
-      <c r="E23" s="91">
+      <c r="E23" s="113">
         <f t="shared" ref="E23:J23" si="5">D23+1</f>
         <v>46297</v>
       </c>
-      <c r="F23" s="17">
+      <c r="F23" s="114">
         <f t="shared" si="5"/>
         <v>46298</v>
       </c>
-      <c r="G23" s="17">
+      <c r="G23" s="114">
         <f t="shared" si="5"/>
         <v>46299</v>
       </c>
-      <c r="H23" s="67">
+      <c r="H23" s="115">
         <f t="shared" si="5"/>
         <v>46300</v>
       </c>
-      <c r="I23" s="17">
+      <c r="I23" s="114">
         <f>H23+1</f>
         <v>46301</v>
       </c>
-      <c r="J23" s="17">
+      <c r="J23" s="114">
         <f t="shared" si="5"/>
         <v>46302</v>
       </c>
-      <c r="K23" s="100">
+      <c r="K23" s="114">
         <f>J23+1</f>
         <v>46303</v>
       </c>
-      <c r="L23" s="16">
+      <c r="L23" s="114">
         <f t="shared" ref="L23:Q23" si="6">K23+1</f>
         <v>46304</v>
       </c>
-      <c r="M23" s="17">
+      <c r="M23" s="114">
         <f t="shared" si="6"/>
         <v>46305</v>
       </c>
-      <c r="N23" s="17">
+      <c r="N23" s="114">
         <f t="shared" si="6"/>
         <v>46306</v>
       </c>
-      <c r="O23" s="17">
+      <c r="O23" s="114">
         <f t="shared" si="6"/>
         <v>46307</v>
       </c>
-      <c r="P23" s="17">
+      <c r="P23" s="114">
         <f t="shared" si="6"/>
         <v>46308</v>
       </c>
-      <c r="Q23" s="17">
+      <c r="Q23" s="114">
         <f t="shared" si="6"/>
         <v>46309</v>
       </c>
-      <c r="R23" s="100">
+      <c r="R23" s="114">
         <f>Q23+1</f>
         <v>46310</v>
       </c>
-      <c r="S23" s="16">
+      <c r="S23" s="114">
         <f t="shared" ref="S23:X23" si="7">R23+1</f>
         <v>46311</v>
       </c>
-      <c r="T23" s="17">
+      <c r="T23" s="114">
         <f t="shared" si="7"/>
         <v>46312</v>
       </c>
-      <c r="U23" s="17">
+      <c r="U23" s="114">
         <f t="shared" si="7"/>
         <v>46313</v>
       </c>
-      <c r="V23" s="17">
+      <c r="V23" s="114">
         <f t="shared" si="7"/>
         <v>46314</v>
       </c>
-      <c r="W23" s="17">
+      <c r="W23" s="114">
         <f t="shared" si="7"/>
         <v>46315</v>
       </c>
-      <c r="X23" s="17">
+      <c r="X23" s="114">
         <f t="shared" si="7"/>
         <v>46316</v>
       </c>
-      <c r="Y23" s="100">
+      <c r="Y23" s="114">
         <f>X23+1</f>
         <v>46317</v>
       </c>
-      <c r="Z23" s="16">
+      <c r="Z23" s="114">
         <f t="shared" ref="Z23:AE23" si="8">Y23+1</f>
         <v>46318</v>
       </c>
-      <c r="AA23" s="17">
+      <c r="AA23" s="114">
         <f t="shared" si="8"/>
         <v>46319</v>
       </c>
-      <c r="AB23" s="17">
+      <c r="AB23" s="114">
         <f t="shared" si="8"/>
         <v>46320</v>
       </c>
-      <c r="AC23" s="17">
+      <c r="AC23" s="114">
         <f t="shared" si="8"/>
         <v>46321</v>
       </c>
-      <c r="AD23" s="17">
+      <c r="AD23" s="114">
         <f t="shared" si="8"/>
         <v>46322</v>
       </c>
-      <c r="AE23" s="17">
+      <c r="AE23" s="114">
         <f t="shared" si="8"/>
         <v>46323</v>
       </c>
-      <c r="AF23" s="100">
+      <c r="AF23" s="114">
         <f>AE23+1</f>
         <v>46324</v>
       </c>
-      <c r="AG23" s="91">
+      <c r="AG23" s="113">
         <f>AF23+1</f>
         <v>46325</v>
       </c>
-      <c r="AH23" s="21">
+      <c r="AH23" s="18">
         <f>AH8</f>
         <v>46326</v>
       </c>
-      <c r="AI23" s="12" t="s">
+      <c r="AI23" s="11" t="s">
         <v>0</v>
       </c>
       <c r="AJ23" s="1">
@@ -5960,37 +5745,37 @@
       <c r="C24" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="D24" s="95"/>
-      <c r="E24" s="92"/>
-      <c r="F24" s="14"/>
-      <c r="G24" s="14"/>
-      <c r="H24" s="68"/>
-      <c r="I24" s="14"/>
-      <c r="J24" s="14"/>
-      <c r="K24" s="101"/>
-      <c r="L24" s="92"/>
-      <c r="M24" s="14"/>
-      <c r="N24" s="14"/>
-      <c r="O24" s="14"/>
-      <c r="P24" s="14"/>
-      <c r="Q24" s="14"/>
-      <c r="R24" s="101"/>
-      <c r="S24" s="92"/>
-      <c r="T24" s="14"/>
-      <c r="U24" s="14"/>
-      <c r="V24" s="14"/>
-      <c r="W24" s="14"/>
-      <c r="X24" s="14"/>
-      <c r="Y24" s="101"/>
-      <c r="Z24" s="92"/>
-      <c r="AA24" s="14"/>
-      <c r="AB24" s="14"/>
-      <c r="AC24" s="14"/>
-      <c r="AD24" s="14"/>
-      <c r="AE24" s="14"/>
-      <c r="AF24" s="101"/>
-      <c r="AG24" s="106"/>
-      <c r="AH24" s="20">
+      <c r="D24" s="116"/>
+      <c r="E24" s="13"/>
+      <c r="F24" s="13"/>
+      <c r="G24" s="13"/>
+      <c r="H24" s="53"/>
+      <c r="I24" s="13"/>
+      <c r="J24" s="13"/>
+      <c r="K24" s="13"/>
+      <c r="L24" s="13"/>
+      <c r="M24" s="13"/>
+      <c r="N24" s="13"/>
+      <c r="O24" s="13"/>
+      <c r="P24" s="13"/>
+      <c r="Q24" s="13"/>
+      <c r="R24" s="13"/>
+      <c r="S24" s="13"/>
+      <c r="T24" s="13"/>
+      <c r="U24" s="13"/>
+      <c r="V24" s="13"/>
+      <c r="W24" s="13"/>
+      <c r="X24" s="13"/>
+      <c r="Y24" s="13"/>
+      <c r="Z24" s="13"/>
+      <c r="AA24" s="13"/>
+      <c r="AB24" s="13"/>
+      <c r="AC24" s="13"/>
+      <c r="AD24" s="13"/>
+      <c r="AE24" s="13"/>
+      <c r="AF24" s="13"/>
+      <c r="AG24" s="13"/>
+      <c r="AH24" s="17">
         <f>AH9</f>
         <v>0</v>
       </c>
@@ -6003,55 +5788,55 @@
       </c>
     </row>
     <row r="25" spans="1:39" ht="17.25" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="C25" s="142"/>
-      <c r="D25" s="143"/>
-      <c r="E25" s="143"/>
-      <c r="F25" s="143"/>
-      <c r="G25" s="143"/>
-      <c r="H25" s="143"/>
-      <c r="I25" s="143"/>
-      <c r="J25" s="143"/>
-      <c r="K25" s="143"/>
-      <c r="L25" s="143"/>
-      <c r="M25" s="143"/>
-      <c r="N25" s="143"/>
-      <c r="O25" s="143"/>
-      <c r="P25" s="143"/>
-      <c r="Q25" s="143"/>
-      <c r="R25" s="143"/>
-      <c r="S25" s="143"/>
-      <c r="T25" s="143"/>
-      <c r="U25" s="143"/>
-      <c r="V25" s="143"/>
-      <c r="W25" s="143"/>
-      <c r="X25" s="143"/>
-      <c r="Y25" s="143"/>
-      <c r="Z25" s="143"/>
-      <c r="AA25" s="143"/>
-      <c r="AB25" s="143"/>
-      <c r="AC25" s="143"/>
-      <c r="AD25" s="143"/>
-      <c r="AE25" s="143"/>
-      <c r="AF25" s="143"/>
-      <c r="AG25" s="143"/>
-      <c r="AH25" s="143"/>
-      <c r="AI25" s="143"/>
+      <c r="C25" s="84"/>
+      <c r="D25" s="85"/>
+      <c r="E25" s="85"/>
+      <c r="F25" s="85"/>
+      <c r="G25" s="85"/>
+      <c r="H25" s="85"/>
+      <c r="I25" s="85"/>
+      <c r="J25" s="85"/>
+      <c r="K25" s="85"/>
+      <c r="L25" s="85"/>
+      <c r="M25" s="85"/>
+      <c r="N25" s="85"/>
+      <c r="O25" s="85"/>
+      <c r="P25" s="85"/>
+      <c r="Q25" s="85"/>
+      <c r="R25" s="85"/>
+      <c r="S25" s="85"/>
+      <c r="T25" s="85"/>
+      <c r="U25" s="85"/>
+      <c r="V25" s="85"/>
+      <c r="W25" s="85"/>
+      <c r="X25" s="85"/>
+      <c r="Y25" s="85"/>
+      <c r="Z25" s="85"/>
+      <c r="AA25" s="85"/>
+      <c r="AB25" s="85"/>
+      <c r="AC25" s="85"/>
+      <c r="AD25" s="85"/>
+      <c r="AE25" s="85"/>
+      <c r="AF25" s="85"/>
+      <c r="AG25" s="85"/>
+      <c r="AH25" s="85"/>
+      <c r="AI25" s="85"/>
       <c r="AM25" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="26" spans="1:39" x14ac:dyDescent="0.45">
-      <c r="C26" s="144"/>
-      <c r="D26" s="144"/>
-      <c r="E26" s="144"/>
+      <c r="C26" s="86"/>
+      <c r="D26" s="86"/>
+      <c r="E26" s="86"/>
     </row>
     <row r="27" spans="1:39" x14ac:dyDescent="0.45">
-      <c r="C27" s="38"/>
+      <c r="C27" s="29"/>
       <c r="D27"/>
     </row>
     <row r="28" spans="1:39" x14ac:dyDescent="0.45">
       <c r="C28" s="2"/>
-      <c r="W28" s="107"/>
+      <c r="W28" s="70"/>
     </row>
     <row r="29" spans="1:39" x14ac:dyDescent="0.45">
       <c r="C29" s="2"/>
@@ -6073,23 +5858,6 @@
     </row>
   </sheetData>
   <mergeCells count="33">
-    <mergeCell ref="B10:B11"/>
-    <mergeCell ref="AL16:AM16"/>
-    <mergeCell ref="B18:B21"/>
-    <mergeCell ref="C25:AI25"/>
-    <mergeCell ref="C26:E26"/>
-    <mergeCell ref="AG2:AG4"/>
-    <mergeCell ref="V2:V4"/>
-    <mergeCell ref="W2:W4"/>
-    <mergeCell ref="X2:X4"/>
-    <mergeCell ref="Y2:Y4"/>
-    <mergeCell ref="Z2:Z4"/>
-    <mergeCell ref="AA2:AA4"/>
-    <mergeCell ref="AB2:AB4"/>
-    <mergeCell ref="AC2:AC4"/>
-    <mergeCell ref="AD2:AD4"/>
-    <mergeCell ref="AE2:AE4"/>
-    <mergeCell ref="AF2:AF4"/>
     <mergeCell ref="U2:U4"/>
     <mergeCell ref="C1:AH1"/>
     <mergeCell ref="C2:C4"/>
@@ -6106,6 +5874,23 @@
     <mergeCell ref="N2:N4"/>
     <mergeCell ref="S2:S4"/>
     <mergeCell ref="T2:T4"/>
+    <mergeCell ref="AG2:AG4"/>
+    <mergeCell ref="V2:V4"/>
+    <mergeCell ref="W2:W4"/>
+    <mergeCell ref="X2:X4"/>
+    <mergeCell ref="Y2:Y4"/>
+    <mergeCell ref="Z2:Z4"/>
+    <mergeCell ref="AA2:AA4"/>
+    <mergeCell ref="AB2:AB4"/>
+    <mergeCell ref="AC2:AC4"/>
+    <mergeCell ref="AD2:AD4"/>
+    <mergeCell ref="AE2:AE4"/>
+    <mergeCell ref="AF2:AF4"/>
+    <mergeCell ref="B10:B11"/>
+    <mergeCell ref="AL16:AM16"/>
+    <mergeCell ref="B18:B21"/>
+    <mergeCell ref="C25:AI25"/>
+    <mergeCell ref="C26:E26"/>
   </mergeCells>
   <phoneticPr fontId="2"/>
   <conditionalFormatting sqref="C7:AH9 C10:C16 C18:C25 O20 O21:P21 D22:AI24 V10">
